--- a/bom/Fall_Protection_Vest_BOM.xlsx
+++ b/bom/Fall_Protection_Vest_BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/phongtruong2003/Desktop/Inflate Body/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDC59AA6-A0FF-E944-AB9F-C2DE4A2101BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42360E3A-38ED-1143-B8FF-D78DCD74E2BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17100" yWindow="680" windowWidth="17100" windowHeight="19800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17100" yWindow="680" windowWidth="17100" windowHeight="19780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EE BOM" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="100">
   <si>
     <t>Fall Protection Vest - EE DigiKey Parts List</t>
   </si>
@@ -206,24 +206,9 @@
     <t>Testing</t>
   </si>
   <si>
-    <t>5 mm LED kit</t>
-  </si>
-  <si>
-    <t>4203 / 1528-2952-ND</t>
-  </si>
-  <si>
-    <t>Show test output</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/adafruit-industries-llc/4203/10130502</t>
-  </si>
-  <si>
     <t>EE Lead</t>
   </si>
   <si>
-    <t>Use before the real valve.</t>
-  </si>
-  <si>
     <t>220 ohm resistor</t>
   </si>
   <si>
@@ -260,42 +245,12 @@
     <t>Power</t>
   </si>
   <si>
-    <t>3.7 V 500 mAh battery</t>
-  </si>
-  <si>
-    <t>1578 / 1528-1841-ND</t>
-  </si>
-  <si>
-    <t>Power the prototype</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/adafruit-industries-llc/1578/5054539</t>
-  </si>
-  <si>
     <t>Buy Later</t>
   </si>
   <si>
     <t>Power / Circuits</t>
   </si>
   <si>
-    <t>Confirm capacity first.</t>
-  </si>
-  <si>
-    <t>USB-C LiPo charger</t>
-  </si>
-  <si>
-    <t>4410 / 1528-4410-ND</t>
-  </si>
-  <si>
-    <t>Charge the battery</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/adafruit-industries-llc/4410/10673110</t>
-  </si>
-  <si>
-    <t>Confirm battery and polarity.</t>
-  </si>
-  <si>
     <t>3.3 V regulator</t>
   </si>
   <si>
@@ -350,21 +305,6 @@
     <t>PCB</t>
   </si>
   <si>
-    <t>Half-size Perma-Proto</t>
-  </si>
-  <si>
-    <t>1609 / 1528-1195-ND</t>
-  </si>
-  <si>
-    <t>Make a soldered circuit</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/adafruit-industries-llc/1609/5353655</t>
-  </si>
-  <si>
-    <t>Use after breadboard testing.</t>
-  </si>
-  <si>
     <t>10 uF capacitor pack</t>
   </si>
   <si>
@@ -381,21 +321,6 @@
   </si>
   <si>
     <t>Choose exact value later.</t>
-  </si>
-  <si>
-    <t>22 AWG hook-up wire set</t>
-  </si>
-  <si>
-    <t>1311 / 1528-1743-ND</t>
-  </si>
-  <si>
-    <t>Wire the final circuit</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/adafruit-industries-llc/1311/6198255</t>
-  </si>
-  <si>
-    <t>Skip if the lab has wire.</t>
   </si>
   <si>
     <t>Category subtotal</t>
@@ -716,7 +641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -755,7 +680,7 @@
     </row>
     <row r="2" spans="1:14" ht="15">
       <c r="A2" s="10" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -777,8 +702,8 @@
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="2">
-        <f>SUMIF($J$7:$J$23,"Buy Now",$I$7:$I$23)</f>
-        <v>59.640000000000015</v>
+        <f>SUMIF($J$7:$J$19,"Buy Now",$I$7:$I$19)</f>
+        <v>54.690000000000012</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="11"/>
@@ -862,7 +787,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" ref="I7:I23" si="0">G7*H7</f>
+        <f t="shared" ref="I7:I18" si="0">G7*H7</f>
         <v>21.44</v>
       </c>
       <c r="J7" s="4" t="s">
@@ -1111,35 +1036,35 @@
         <v>56</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>20</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G13" s="5">
-        <v>4.95</v>
+        <v>0.11</v>
       </c>
       <c r="H13" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="0"/>
-        <v>4.95</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>22</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L13" s="4" t="s">
         <v>24</v>
@@ -1171,26 +1096,26 @@
         <v>66</v>
       </c>
       <c r="G14" s="5">
-        <v>0.11</v>
+        <v>0.95</v>
       </c>
       <c r="H14" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
+        <v>0.95</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>22</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="N14" s="4" t="s">
         <v>26</v>
@@ -1198,44 +1123,44 @@
     </row>
     <row r="15" spans="1:14" ht="52" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>20</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G15" s="5">
-        <v>0.95</v>
+        <v>2.25</v>
       </c>
       <c r="H15" s="6">
         <v>1</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" si="0"/>
-        <v>0.95</v>
+        <v>2.25</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="N15" s="4" t="s">
         <v>26</v>
@@ -1243,44 +1168,44 @@
     </row>
     <row r="16" spans="1:14" ht="52" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>20</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G16" s="5">
-        <v>7.95</v>
+        <v>2.88</v>
       </c>
       <c r="H16" s="6">
         <v>1</v>
       </c>
       <c r="I16" s="5">
         <f t="shared" si="0"/>
-        <v>7.95</v>
+        <v>2.88</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="L16" s="4" t="s">
         <v>24</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="N16" s="4" t="s">
         <v>26</v>
@@ -1288,44 +1213,44 @@
     </row>
     <row r="17" spans="1:14" ht="52" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>20</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G17" s="5">
-        <v>5.95</v>
+        <v>2.95</v>
       </c>
       <c r="H17" s="6">
         <v>1</v>
       </c>
       <c r="I17" s="5">
         <f t="shared" si="0"/>
-        <v>5.95</v>
+        <v>2.95</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="L17" s="4" t="s">
         <v>24</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="N17" s="4" t="s">
         <v>26</v>
@@ -1333,363 +1258,154 @@
     </row>
     <row r="18" spans="1:14" ht="52" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>20</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G18" s="5">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="H18" s="6">
         <v>1</v>
       </c>
       <c r="I18" s="5">
         <f t="shared" si="0"/>
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="N18" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="52" customHeight="1">
-      <c r="A19" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D19" s="4" t="s">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="4"/>
+      <c r="N19" s="4"/>
+    </row>
+    <row r="22" spans="1:14" ht="15">
+      <c r="A22" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E19" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F19" s="8" t="s">
+      <c r="B22" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="G19" s="5">
-        <v>2.88</v>
-      </c>
-      <c r="H19" s="6">
-        <v>1</v>
-      </c>
-      <c r="I19" s="5">
-        <f t="shared" si="0"/>
-        <v>2.88</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="L19" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M19" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="N19" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="52" customHeight="1">
-      <c r="A20" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="G20" s="5">
-        <v>2.95</v>
-      </c>
-      <c r="H20" s="6">
-        <v>1</v>
-      </c>
-      <c r="I20" s="5">
-        <f t="shared" si="0"/>
-        <v>2.95</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="L20" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M20" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="N20" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="52" customHeight="1">
-      <c r="A21" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="G21" s="5">
-        <v>4.5</v>
-      </c>
-      <c r="H21" s="6">
-        <v>1</v>
-      </c>
-      <c r="I21" s="5">
-        <f t="shared" si="0"/>
-        <v>4.5</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="L21" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M21" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="N21" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="52" customHeight="1">
-      <c r="A22" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="G22" s="5">
-        <v>1.95</v>
-      </c>
-      <c r="H22" s="6">
-        <v>1</v>
-      </c>
-      <c r="I22" s="5">
-        <f t="shared" si="0"/>
-        <v>1.95</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="K22" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="L22" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="M22" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="N22" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="52" customHeight="1">
-      <c r="A23" s="4" t="s">
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" s="7">
+        <f>SUMIF($A$7:$A$19,A23,$I$7:$I$19)</f>
+        <v>21.44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" s="7">
+        <f>SUMIF($A$7:$A$19,A24,$I$7:$I$19)</f>
+        <v>19.95</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="G23" s="5">
-        <v>15.95</v>
-      </c>
-      <c r="H23" s="6">
-        <v>1</v>
-      </c>
-      <c r="I23" s="5">
-        <f t="shared" si="0"/>
-        <v>15.95</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="K23" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="L23" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M23" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="N23" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" ht="15">
-      <c r="A26" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
+      <c r="B25" s="7">
+        <f>SUMIF($A$7:$A$19,A25,$I$7:$I$19)</f>
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="7">
+        <f>SUMIF($A$7:$A$19,A26,$I$7:$I$19)</f>
+        <v>6.9</v>
+      </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="B27" s="7">
-        <f t="shared" ref="B27:B34" si="1">SUMIF($A$7:$A$23,A27,$I$7:$I$23)</f>
-        <v>21.44</v>
+        <f>SUMIF($A$7:$A$19,A27,$I$7:$I$19)</f>
+        <v>1.5</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="B28" s="7">
-        <f t="shared" si="1"/>
-        <v>19.95</v>
+        <f>SUMIF($A$7:$A$19,A28,$I$7:$I$19)</f>
+        <v>4.2</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="B29" s="7">
-        <f t="shared" si="1"/>
-        <v>20.85</v>
+        <f>SUMIF($A$7:$A$19,A29,$I$7:$I$19)</f>
+        <v>5.83</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="B30" s="7">
-        <f t="shared" si="1"/>
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
-      <c r="A31" t="s">
-        <v>56</v>
-      </c>
-      <c r="B31" s="7">
-        <f t="shared" si="1"/>
-        <v>6.45</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14">
-      <c r="A32" t="s">
-        <v>74</v>
-      </c>
-      <c r="B32" s="7">
-        <f t="shared" si="1"/>
-        <v>18.099999999999998</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" t="s">
-        <v>93</v>
-      </c>
-      <c r="B33" s="7">
-        <f t="shared" si="1"/>
-        <v>5.83</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" t="s">
-        <v>104</v>
-      </c>
-      <c r="B34" s="7">
-        <f t="shared" si="1"/>
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" ht="15">
-      <c r="A36" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B36" s="2">
-        <f>SUM($I$7:$I$23)</f>
-        <v>104.02000000000002</v>
+        <f>SUMIF($A$7:$A$19,A30,$I$7:$I$19)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="15">
+      <c r="A32" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B32" s="2">
+        <f>SUM($I$7:$I$19)</f>
+        <v>64.720000000000013</v>
       </c>
     </row>
   </sheetData>
@@ -1702,10 +1418,10 @@
     <mergeCell ref="K4:L4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="J7:J23" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="J7:J19" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Buy Now,Buy Later"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="K7:K23" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" sqref="K7:K19" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"EE Lead,Firmware / MCU / IMU,Power / Circuits,PCB / Hardware"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1716,17 +1432,12 @@
     <hyperlink ref="F10" r:id="rId4" xr:uid="{E6873BA5-8123-9744-8086-F161B8C6D769}"/>
     <hyperlink ref="F11" r:id="rId5" xr:uid="{237FE88B-6105-1146-9C63-FEB16F602235}"/>
     <hyperlink ref="F12" r:id="rId6" xr:uid="{79784A41-6B3E-3642-9A9A-1939C54448B8}"/>
-    <hyperlink ref="F13" r:id="rId7" xr:uid="{6AA8653C-ED77-8A4D-8CF1-24D6F289F652}"/>
-    <hyperlink ref="F14" r:id="rId8" xr:uid="{78FA2453-D9B7-844F-AF3C-CC1DC02893AC}"/>
-    <hyperlink ref="F15" r:id="rId9" xr:uid="{CBD6832D-626B-6947-BF62-37E6EAB77CD6}"/>
-    <hyperlink ref="F16" r:id="rId10" xr:uid="{0BE43668-3BD4-4541-BAA2-570BEC1C513F}"/>
-    <hyperlink ref="F17" r:id="rId11" xr:uid="{9AA5BEBA-A7EB-1A4B-BCD1-5105CF775510}"/>
-    <hyperlink ref="F18" r:id="rId12" xr:uid="{880332A3-D478-684C-B133-9E42F4ABD33D}"/>
-    <hyperlink ref="F19" r:id="rId13" xr:uid="{89BCA23B-ECC0-904A-8D22-E178C590347E}"/>
-    <hyperlink ref="F20" r:id="rId14" xr:uid="{3DDCB3E9-A6B4-5C4A-ADA0-2F88EA41B926}"/>
-    <hyperlink ref="F21" r:id="rId15" xr:uid="{6CC672C0-DA75-4C4A-BB94-0DA855C2814C}"/>
-    <hyperlink ref="F22" r:id="rId16" xr:uid="{EC2FEB3A-0512-9340-B9D3-19FD6E14CF7B}"/>
-    <hyperlink ref="F23" r:id="rId17" xr:uid="{CEB78387-557A-5843-A0F3-AB3C8724A419}"/>
+    <hyperlink ref="F13" r:id="rId7" xr:uid="{78FA2453-D9B7-844F-AF3C-CC1DC02893AC}"/>
+    <hyperlink ref="F14" r:id="rId8" xr:uid="{CBD6832D-626B-6947-BF62-37E6EAB77CD6}"/>
+    <hyperlink ref="F15" r:id="rId9" xr:uid="{880332A3-D478-684C-B133-9E42F4ABD33D}"/>
+    <hyperlink ref="F16" r:id="rId10" xr:uid="{89BCA23B-ECC0-904A-8D22-E178C590347E}"/>
+    <hyperlink ref="F17" r:id="rId11" xr:uid="{3DDCB3E9-A6B4-5C4A-ADA0-2F88EA41B926}"/>
+    <hyperlink ref="F18" r:id="rId12" xr:uid="{EC2FEB3A-0512-9340-B9D3-19FD6E14CF7B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bom/Fall_Protection_Vest_BOM.xlsx
+++ b/bom/Fall_Protection_Vest_BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/phongtruong2003/Desktop/Inflate Body/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42360E3A-38ED-1143-B8FF-D78DCD74E2BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D6520C9-16C8-6249-AB6E-753F532F7E58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17100" yWindow="680" windowWidth="17100" windowHeight="19780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17100" yWindow="680" windowWidth="17100" windowHeight="19860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EE BOM" sheetId="1" r:id="rId1"/>
@@ -33,9 +33,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="100">
-  <si>
-    <t>Fall Protection Vest - EE DigiKey Parts List</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="99">
+  <si>
+    <t>Note: Shipping, tax, not included.</t>
   </si>
   <si>
     <t>Buy Now total</t>
@@ -56,9 +56,6 @@
     <t>Shop</t>
   </si>
   <si>
-    <t>DigiKey Link</t>
-  </si>
-  <si>
     <t>Unit Price</t>
   </si>
   <si>
@@ -152,78 +149,15 @@
     <t>For I2C wiring.</t>
   </si>
   <si>
-    <t>USB A to USB-C cable</t>
-  </si>
-  <si>
-    <t>4473 / 1528-4473-ND</t>
-  </si>
-  <si>
-    <t>Program the board</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/adafruit-industries-llc/4473/11587356</t>
-  </si>
-  <si>
-    <t>Fits the board USB-C port.</t>
-  </si>
-  <si>
     <t>Prototyping</t>
   </si>
   <si>
-    <t>Half-size breadboard</t>
-  </si>
-  <si>
-    <t>Adafruit 64</t>
-  </si>
-  <si>
-    <t>Build test circuits</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/adafruit-industries-llc/64/7241427</t>
-  </si>
-  <si>
-    <t>PCB / Hardware</t>
-  </si>
-  <si>
-    <t>Reusable for testing.</t>
-  </si>
-  <si>
-    <t>Male jumper wires</t>
-  </si>
-  <si>
-    <t>1956 / 1528-1966-ND</t>
-  </si>
-  <si>
-    <t>Connect parts</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/adafruit-industries-llc/1956/6827089</t>
-  </si>
-  <si>
-    <t>20-wire pack.</t>
-  </si>
-  <si>
     <t>Testing</t>
   </si>
   <si>
     <t>EE Lead</t>
   </si>
   <si>
-    <t>220 ohm resistor</t>
-  </si>
-  <si>
-    <t>CFR-25JB-52-220R / 220QBK-ND</t>
-  </si>
-  <si>
-    <t>Protect the LED</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/yageo/CFR-25JB-52-220R/1295</t>
-  </si>
-  <si>
-    <t>Five pieces for testing.</t>
-  </si>
-  <si>
     <t>5 V buzzer</t>
   </si>
   <si>
@@ -245,12 +179,27 @@
     <t>Power</t>
   </si>
   <si>
+    <t>3.7 V 500 mAh battery</t>
+  </si>
+  <si>
+    <t>1578 / 1528-1841-ND</t>
+  </si>
+  <si>
+    <t>Power the prototype</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/adafruit-industries-llc/1578/5054539</t>
+  </si>
+  <si>
     <t>Buy Later</t>
   </si>
   <si>
     <t>Power / Circuits</t>
   </si>
   <si>
+    <t>Confirm capacity first.</t>
+  </si>
+  <si>
     <t>3.3 V regulator</t>
   </si>
   <si>
@@ -305,34 +254,82 @@
     <t>PCB</t>
   </si>
   <si>
-    <t>10 uF capacitor pack</t>
-  </si>
-  <si>
-    <t>2195 / 1528-2195-ND</t>
-  </si>
-  <si>
-    <t>Smooth the power</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/adafruit-industries-llc/2195/26744569</t>
-  </si>
-  <si>
-    <t>Out of stock</t>
-  </si>
-  <si>
-    <t>Choose exact value later.</t>
+    <t>Fall Protection Vest - EE Parts List</t>
+  </si>
+  <si>
+    <t>Product Link</t>
+  </si>
+  <si>
+    <t>Optional / Future Features</t>
+  </si>
+  <si>
+    <t>Arduino UNO R4 WiFi</t>
+  </si>
+  <si>
+    <t>ABX00087 / UNO R4 WiFi</t>
+  </si>
+  <si>
+    <t>Optional controller for communication tests</t>
+  </si>
+  <si>
+    <t>Arduino Store</t>
+  </si>
+  <si>
+    <t>https://store.arduino.cc/products/uno-r4-wifi</t>
+  </si>
+  <si>
+    <t>Optional</t>
+  </si>
+  <si>
+    <t>Prototype alternative only; the main design remains Cortex-M33.</t>
+  </si>
+  <si>
+    <t>9/8/2026</t>
+  </si>
+  <si>
+    <t>SIM800L GSM module</t>
+  </si>
+  <si>
+    <t>Optional cellular communication prototype</t>
+  </si>
+  <si>
+    <t>Common module vendor</t>
+  </si>
+  <si>
+    <t>2G GSM prototype module only. 2G availability varies by region; verify local carrier support before buying.</t>
+  </si>
+  <si>
+    <t>NEO-6M GPS module</t>
+  </si>
+  <si>
+    <t>u-blox NEO-6M / GY-NEO6MV2</t>
+  </si>
+  <si>
+    <t>Optional location tracking prototype</t>
+  </si>
+  <si>
+    <t>GPS prototype module; confirm antenna, voltage, and UART connection before buying.</t>
   </si>
   <si>
     <t>Category subtotal</t>
   </si>
   <si>
-    <t>Amount</t>
-  </si>
-  <si>
     <t>EE material total</t>
   </si>
   <si>
-    <t>Note: Shipping, tax, not included.</t>
+    <t>Testing change</t>
+  </si>
+  <si>
+    <t>Power change</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/HiLetgo-Smallest-Breakout-Quad-band-3-7-4-2V/dp/B01DLIJM2E/ref=sr_1_1?dib=eyJ2IjoiMSJ9.ABq9RwpR4zEaRP94WYhaZsse_g4wLKG886CfPnOovAL9IGpiJxZt1vDdeBNCKHM7Ox4FdodN3aDBWp92LAojHDmLq2A43oF2IaAbBOXKgH2al5nzrgpl1UIKkn174-Lgwmx9OFjCekA2H7DFQFQpqAJMfifR0TagpXn93sFxzyaNOwUpCdIb_3MHKk9gdFKUetyWoc-WObQnP5-WA4xhWnbeMDDpDrGVpzyGzqH1yxs.n3ItyVcx8VlaJ5Q8SgjHAqBSqVgZd35zt-cdIA4uVrs&amp;dib_tag=se&amp;keywords=sim800l&amp;qid=1788911984&amp;sr=8-1&amp;th=1</t>
+  </si>
+  <si>
+    <t>SIM800L GPRS GSM Breakout Module</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/YELUFT-GY-NEO6MV2-Control-Support-Raspberry/dp/B0F2DKWJ4J/ref=sr_1_5?crid=116EGIA65O3RM&amp;dib=eyJ2IjoiMSJ9._JPp2AFGHWD_4dT5XNP-SnycfWRcMEOIub2ZYPONWQCLCLeiU7IqwyEKS3O7elcKxsS4py1gFeZ29XIWHm3QTQ3QX_M8mEECUlKve1ZeAJ8Sea1zyersA8alZieFz783-0tomvuy7tnT7_plsjbRSkmZne4iC7YSXRxw8aODNDlKrBKc52KSxYyvh4mKNzSCc9jvfxMSm6pLkugQCZksvUxxBY3AoB3QW4X--jUrNn5T5i-aCIDrq5RVg4QEaVsgrToN-ionJzHsbWyn2QLOyEeYSgOXiigk-v-RNM3CDFg.Pa5G0Wery0aCEinKh-zrDlm7cRXMrO8CM8Sp6U33dIg&amp;dib_tag=se&amp;keywords=neo%2B6m&amp;qid=1788912414&amp;sprefix=%2Caps%2C165&amp;sr=8-5&amp;th=1</t>
   </si>
 </sst>
 </file>
@@ -342,7 +339,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -365,9 +362,19 @@
       <name val="Carlito"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -401,7 +408,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -417,10 +424,22 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -430,7 +449,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -641,7 +660,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -661,63 +680,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="19">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+    </row>
+    <row r="2" spans="1:14" ht="15">
+      <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-    </row>
-    <row r="2" spans="1:14" ht="15">
-      <c r="A2" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
     </row>
     <row r="4" spans="1:14" ht="15">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="11"/>
+      <c r="B4" s="17"/>
       <c r="C4" s="2">
-        <f>SUMIF($J$7:$J$19,"Buy Now",$I$7:$I$19)</f>
-        <v>54.690000000000012</v>
+        <f>SUMIF($J$7:$J$17,"Buy Now",$I$7:$I$17)</f>
+        <v>43.290000000000006</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
       <c r="G4" s="2"/>
       <c r="H4" s="1"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
     </row>
-    <row r="6" spans="1:14" ht="36" customHeight="1">
+    <row r="6" spans="1:14" ht="48" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
@@ -734,51 +753,51 @@
         <v>6</v>
       </c>
       <c r="F6" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="I6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="K6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="L6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L6" s="3" t="s">
+      <c r="M6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="M6" s="3" t="s">
+      <c r="N6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="N6" s="3" t="s">
+    </row>
+    <row r="7" spans="1:14" ht="69.25" customHeight="1">
+      <c r="A7" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" ht="52" customHeight="1">
-      <c r="A7" s="4" t="s">
+      <c r="B7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="C7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="F7" s="7" t="s">
         <v>20</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>21</v>
       </c>
       <c r="G7" s="5">
         <v>21.44</v>
@@ -787,43 +806,43 @@
         <v>1</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" ref="I7:I18" si="0">G7*H7</f>
+        <f t="shared" ref="I7:I14" si="0">G7*H7</f>
         <v>21.44</v>
       </c>
       <c r="J7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="L7" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="L7" s="4" t="s">
+      <c r="M7" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="M7" s="4" t="s">
+      <c r="N7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="N7" s="4" t="s">
+    </row>
+    <row r="8" spans="1:14" ht="69.25" customHeight="1">
+      <c r="A8" s="4" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" ht="52" customHeight="1">
-      <c r="A8" s="4" t="s">
+      <c r="B8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="C8" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>30</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>31</v>
       </c>
       <c r="G8" s="5">
         <v>19.95</v>
@@ -836,39 +855,39 @@
         <v>19.95</v>
       </c>
       <c r="J8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K8" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="L8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="L8" s="4" t="s">
-        <v>24</v>
-      </c>
       <c r="M8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="69.25" customHeight="1">
+      <c r="A9" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="N8" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="52" customHeight="1">
-      <c r="A9" s="4" t="s">
+      <c r="B9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="E9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>36</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="G9" s="5">
         <v>0.95</v>
@@ -881,531 +900,494 @@
         <v>0.95</v>
       </c>
       <c r="J9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="L9" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="L9" s="4" t="s">
-        <v>24</v>
-      </c>
       <c r="M9" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="52" customHeight="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="69.25" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>33</v>
+        <v>94</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>42</v>
+        <v>19</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="G10" s="5">
-        <v>3.95</v>
+        <v>0.95</v>
       </c>
       <c r="H10" s="6">
         <v>1</v>
       </c>
       <c r="I10" s="5">
         <f t="shared" si="0"/>
-        <v>3.95</v>
+        <v>0.95</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="52" customHeight="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="69.25" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>48</v>
+        <v>19</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="G11" s="5">
-        <v>4.95</v>
+        <v>7.95</v>
       </c>
       <c r="H11" s="6">
         <v>1</v>
       </c>
       <c r="I11" s="5">
         <f t="shared" si="0"/>
-        <v>4.95</v>
+        <v>7.95</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="52" customHeight="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="69.25" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>54</v>
+        <v>19</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>58</v>
       </c>
       <c r="G12" s="5">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="H12" s="6">
         <v>1</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="0"/>
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="52" customHeight="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="69.25" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>61</v>
+        <v>19</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="G13" s="5">
-        <v>0.11</v>
+        <v>2.88</v>
       </c>
       <c r="H13" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
+        <v>2.88</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="N13" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="52" customHeight="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="69.25" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>66</v>
+        <v>19</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>70</v>
       </c>
       <c r="G14" s="5">
-        <v>0.95</v>
+        <v>2.95</v>
       </c>
       <c r="H14" s="6">
         <v>1</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="0"/>
-        <v>0.95</v>
+        <v>2.95</v>
       </c>
       <c r="J14" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="N14" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="69.25" customHeight="1">
+      <c r="A15" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G15" s="10">
+        <v>27.5</v>
+      </c>
+      <c r="H15" s="11">
+        <v>1</v>
+      </c>
+      <c r="I15" s="10">
+        <f>G15*H15</f>
+        <v>27.5</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="K15" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="K14" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="L14" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="M14" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="N14" s="4" t="s">
+      <c r="L15" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="M15" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="N15" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="69.25" customHeight="1">
+      <c r="A16" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G16" s="10">
+        <v>8.99</v>
+      </c>
+      <c r="H16" s="11">
+        <v>1</v>
+      </c>
+      <c r="I16" s="10">
+        <f>8.99</f>
+        <v>8.99</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="M16" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="N16" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="69.25" customHeight="1">
+      <c r="A17" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G17" s="10">
+        <v>11.99</v>
+      </c>
+      <c r="H17" s="11">
+        <v>2</v>
+      </c>
+      <c r="I17" s="10">
+        <f>11.99</f>
+        <v>11.99</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="M17" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="N17" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="B18" t="str">
+        <f t="shared" ref="B18:B25" si="1">""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="B19" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="15">
+      <c r="A20" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B20" s="14" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="8" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" ht="52" customHeight="1">
-      <c r="A15" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B15" s="4" t="s">
+      <c r="B22" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="12">
+        <f>SUMIF($A$7:$A$17,A26,$I$7:$I$17)</f>
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" s="12">
+        <f>SUMIF($A$7:$A$17,A27,$I$7:$I$17)</f>
+        <v>5.83</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F15" s="8" t="s">
+      <c r="B28" s="12">
+        <f>SUMIF($A$7:$A$17,A28,$I$7:$I$17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="G15" s="5">
-        <v>2.25</v>
-      </c>
-      <c r="H15" s="6">
-        <v>1</v>
-      </c>
-      <c r="I15" s="5">
-        <f t="shared" si="0"/>
-        <v>2.25</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="L15" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="M15" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="N15" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="52" customHeight="1">
-      <c r="A16" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="G16" s="5">
-        <v>2.88</v>
-      </c>
-      <c r="H16" s="6">
-        <v>1</v>
-      </c>
-      <c r="I16" s="5">
-        <f t="shared" si="0"/>
-        <v>2.88</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="L16" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M16" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="N16" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="52" customHeight="1">
-      <c r="A17" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="G17" s="5">
-        <v>2.95</v>
-      </c>
-      <c r="H17" s="6">
-        <v>1</v>
-      </c>
-      <c r="I17" s="5">
-        <f t="shared" si="0"/>
-        <v>2.95</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="L17" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M17" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="N17" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="52" customHeight="1">
-      <c r="A18" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F18" s="8" t="s">
+      <c r="B29" s="12">
+        <f>SUMIF($A$7:$A$17,A29,$I$7:$I$17)</f>
+        <v>48.480000000000004</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
+    </row>
+    <row r="31" spans="1:14" ht="15">
+      <c r="A31" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="G18" s="5">
-        <v>1.95</v>
-      </c>
-      <c r="H18" s="6">
-        <v>1</v>
-      </c>
-      <c r="I18" s="5">
-        <f t="shared" si="0"/>
-        <v>1.95</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="L18" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="M18" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="N18" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="52" customHeight="1">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
-      <c r="N19" s="4"/>
-    </row>
-    <row r="22" spans="1:14" ht="15">
-      <c r="A22" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-    </row>
-    <row r="23" spans="1:14">
-      <c r="A23" t="s">
-        <v>16</v>
-      </c>
-      <c r="B23" s="7">
-        <f>SUMIF($A$7:$A$19,A23,$I$7:$I$19)</f>
-        <v>21.44</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
-      <c r="A24" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24" s="7">
-        <f>SUMIF($A$7:$A$19,A24,$I$7:$I$19)</f>
-        <v>19.95</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
-      <c r="A25" t="s">
-        <v>33</v>
-      </c>
-      <c r="B25" s="7">
-        <f>SUMIF($A$7:$A$19,A25,$I$7:$I$19)</f>
-        <v>4.9000000000000004</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
-      <c r="A26" t="s">
-        <v>44</v>
-      </c>
-      <c r="B26" s="7">
-        <f>SUMIF($A$7:$A$19,A26,$I$7:$I$19)</f>
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14">
-      <c r="A27" t="s">
-        <v>56</v>
-      </c>
-      <c r="B27" s="7">
-        <f>SUMIF($A$7:$A$19,A27,$I$7:$I$19)</f>
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14">
-      <c r="A28" t="s">
-        <v>69</v>
-      </c>
-      <c r="B28" s="7">
-        <f>SUMIF($A$7:$A$19,A28,$I$7:$I$19)</f>
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14">
-      <c r="A29" t="s">
-        <v>78</v>
-      </c>
-      <c r="B29" s="7">
-        <f>SUMIF($A$7:$A$19,A29,$I$7:$I$19)</f>
-        <v>5.83</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14">
-      <c r="A30" t="s">
-        <v>89</v>
-      </c>
-      <c r="B30" s="7">
-        <f>SUMIF($A$7:$A$19,A30,$I$7:$I$19)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" ht="15">
-      <c r="A32" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B32" s="2">
-        <f>SUM($I$7:$I$19)</f>
-        <v>64.720000000000013</v>
+      <c r="B31" s="14">
+        <f>SUM($I$7:$I$17)</f>
+        <v>107.80000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1417,27 +1399,25 @@
     <mergeCell ref="I4:J4"/>
     <mergeCell ref="K4:L4"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" sqref="J7:J19" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations disablePrompts="1" count="2">
+    <dataValidation type="list" sqref="J7:J17" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Buy Now,Buy Later"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="K7:K19" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" sqref="K7:K17" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"EE Lead,Firmware / MCU / IMU,Power / Circuits,PCB / Hardware"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="F7" r:id="rId1" xr:uid="{D1E8AC85-9E7C-2E4D-BA4B-CE1D3A69B232}"/>
-    <hyperlink ref="F8" r:id="rId2" xr:uid="{3E304DF1-5B11-2F44-AE00-92E5D4311113}"/>
-    <hyperlink ref="F9" r:id="rId3" xr:uid="{A54E626A-D7E0-F742-8DD4-462BCBDA0EF2}"/>
-    <hyperlink ref="F10" r:id="rId4" xr:uid="{E6873BA5-8123-9744-8086-F161B8C6D769}"/>
-    <hyperlink ref="F11" r:id="rId5" xr:uid="{237FE88B-6105-1146-9C63-FEB16F602235}"/>
-    <hyperlink ref="F12" r:id="rId6" xr:uid="{79784A41-6B3E-3642-9A9A-1939C54448B8}"/>
-    <hyperlink ref="F13" r:id="rId7" xr:uid="{78FA2453-D9B7-844F-AF3C-CC1DC02893AC}"/>
-    <hyperlink ref="F14" r:id="rId8" xr:uid="{CBD6832D-626B-6947-BF62-37E6EAB77CD6}"/>
-    <hyperlink ref="F15" r:id="rId9" xr:uid="{880332A3-D478-684C-B133-9E42F4ABD33D}"/>
-    <hyperlink ref="F16" r:id="rId10" xr:uid="{89BCA23B-ECC0-904A-8D22-E178C590347E}"/>
-    <hyperlink ref="F17" r:id="rId11" xr:uid="{3DDCB3E9-A6B4-5C4A-ADA0-2F88EA41B926}"/>
-    <hyperlink ref="F18" r:id="rId12" xr:uid="{EC2FEB3A-0512-9340-B9D3-19FD6E14CF7B}"/>
+    <hyperlink ref="F7" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="F8" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="F9" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="F10" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="F11" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="F12" r:id="rId6" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="F13" r:id="rId7" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="F14" r:id="rId8" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="F15" r:id="rId9" xr:uid="{59F68FD3-216E-984C-8AA4-3C41D0297640}"/>
+    <hyperlink ref="F16" r:id="rId10" display="https://www.amazon.com/HiLetgo-Smallest-Breakout-Quad-band-3-7-4-2V/dp/B01DLIJM2E/ref=sr_1_1?dib=eyJ2IjoiMSJ9.ABq9RwpR4zEaRP94WYhaZsse_g4wLKG886CfPnOovAL9IGpiJxZt1vDdeBNCKHM7Ox4FdodN3aDBWp92LAojHDmLq2A43oF2IaAbBOXKgH2al5nzrgpl1UIKkn174-Lgwmx9OFjCekA2H7DFQFQpqAJMfifR0TagpXn93sFxzyaNOwUpCdIb_3MHKk9gdFKUetyWoc-WObQnP5-WA4xhWnbeMDDpDrGVpzyGzqH1yxs.n3ItyVcx8VlaJ5Q8SgjHAqBSqVgZd35zt-cdIA4uVrs&amp;dib_tag=se&amp;keywords=sim800l&amp;qid=1788911984&amp;sr=8-1&amp;th=1" xr:uid="{B421DA45-BF02-2445-AAC6-DB60D510EDB7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
